--- a/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:30:34+00:00</t>
+    <t>2026-06-16T13:53:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T13:53:28+00:00</t>
+    <t>2026-06-16T14:51:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:51:07+00:00</t>
+    <t>2026-06-17T12:15:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T12:15:06+00:00</t>
+    <t>2026-06-17T13:49:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T13:49:22+00:00</t>
+    <t>2026-06-17T15:07:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T15:07:59+00:00</t>
+    <t>2026-06-17T15:48:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T15:48:42+00:00</t>
+    <t>2026-06-18T10:03:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T10:03:06+00:00</t>
+    <t>2026-06-18T13:10:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:10:23+00:00</t>
+    <t>2026-06-18T14:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:01:22+00:00</t>
+    <t>2026-06-22T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:03:44+00:00</t>
+    <t>2026-06-22T08:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:16:05+00:00</t>
+    <t>2026-06-22T09:23:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-cda-laboratoire-executant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:23:37+00:00</t>
+    <t>2026-06-22T09:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
